--- a/data/nomenclature.xlsx
+++ b/data/nomenclature.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ParseNSI\data\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NSI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939CD065-E1BA-425C-9A3A-1BE4F63F6A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB35363F-6135-4902-B910-71514F9E7456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="3375" windowWidth="21600" windowHeight="11295" xr2:uid="{B6179685-600B-43B7-9873-FF275DBDA963}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B6179685-600B-43B7-9873-FF275DBDA963}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>артикул</t>
   </si>
@@ -112,13 +112,112 @@
   </si>
   <si>
     <t>GUID</t>
+  </si>
+  <si>
+    <t>Болт 4-14-Ан.Окс-ОСТ 1 31141-80</t>
+  </si>
+  <si>
+    <t>Болт 5-16-Ц-ОСТ 1 31140-80</t>
+  </si>
+  <si>
+    <t>Винт 4-10-Кд.фос.окс-ОСТ 1 31552-80</t>
+  </si>
+  <si>
+    <t>Винт 3-6-Кд-ОСТ 1 31509-80</t>
+  </si>
+  <si>
+    <t>Винт 3-12-Хим.Пас-ОСТ 1 31509-80</t>
+  </si>
+  <si>
+    <t>Винт 4-10-Кд-ОСТ 1 31541-80</t>
+  </si>
+  <si>
+    <t>Винт 4-10-Бп-ОСТ 1 31541-80</t>
+  </si>
+  <si>
+    <t>Винт 4-30-Кд-ОСТ 1 31503-80</t>
+  </si>
+  <si>
+    <t>Винт 5-26-Бп-ОСТ 1 31503-80</t>
+  </si>
+  <si>
+    <t>Винт 8-12-Кд-ОСТ 1 31509-80</t>
+  </si>
+  <si>
+    <t>Винт 5-26-Хим.Пас-ОСТ 1 31503-80</t>
+  </si>
+  <si>
+    <t>7594602323.001</t>
+  </si>
+  <si>
+    <t>7594612323.001</t>
+  </si>
+  <si>
+    <t>7594602323.002</t>
+  </si>
+  <si>
+    <t>7594612323.002</t>
+  </si>
+  <si>
+    <t>7594602323.003</t>
+  </si>
+  <si>
+    <t>7594612323.003</t>
+  </si>
+  <si>
+    <t>7594602323.004</t>
+  </si>
+  <si>
+    <t>7594612323.004</t>
+  </si>
+  <si>
+    <t>7594602323.005</t>
+  </si>
+  <si>
+    <t>7594612323.005</t>
+  </si>
+  <si>
+    <t>7594602323.006</t>
+  </si>
+  <si>
+    <t>7594612323.006</t>
+  </si>
+  <si>
+    <t>Болт 5-16-Ц-ОСТ 1 31140-80                               нет ошибок</t>
+  </si>
+  <si>
+    <t>Винт 4-10-Кд.фос.окс-ОСТ 1 31552-80             нет ошибок</t>
+  </si>
+  <si>
+    <t>Винт 3-6-Кд-ОСТ 1 31509-80                              Винт 3-6-Н.Кд-ОСТ 1 31509-80 некорректное обозначение покрытия, для стали 14Х17Н2 применяется не «Кадмиевое с радужным хроматированием» (Кд), а «Кадмиевое с подслоем никеля, с последующей термической обработкой с радужным хроматированием» (Н.Кд). </t>
+  </si>
+  <si>
+    <t>Винт 3-12-Хим.Пас-ОСТ 1 31509-80                 нет ошибок</t>
+  </si>
+  <si>
+    <t>Винт 4-10-Кд-ОСТ 1 31541-80                           некорректное обозначение покрытия. ОСТ 1 31541-80 соответствует алюминиевому сплаву Д1П, для которого не предусмотрено «Кд», только Ан.Окс и Хим.Окс.</t>
+  </si>
+  <si>
+    <t>Винт 4-10-Бп-ОСТ 1 31541-80                           нет ошибок</t>
+  </si>
+  <si>
+    <t>Винт 4-30-Кд-ОСТ 1 31503-80                           Винт 4-30-Н.Кд-ОСТ 1 31503-80 некорректное обозначение покрытия, для стали 14Х17Н2 применяется не «Кадмиевое с радужным хроматированием» (Кд), а «Кадмиевое с подслоем никеля, с последующей термической обработкой с радужным хроматированием» (Н.Кд).</t>
+  </si>
+  <si>
+    <t>Винт 5-26-Бп-ОСТ 1 31503-80                           нет ошибок</t>
+  </si>
+  <si>
+    <t>Винт 8-12-Кд-ОСТ 1 31509-80                           Винт 8-12-Н.Кд-ОСТ 1 31509-80 некорректное обозначение покрытия, для стали 14Х17Н2 применяется не «Кадмиевое с радужным хроматированием» (Кд), а «Кадмиевое с подслоем никеля, с последующей термической обработкой с радужным хроматированием» (Н.Кд).</t>
+  </si>
+  <si>
+    <t>Винт 5-26-Хим.Пас-ОСТ 1 31503-80                 нет ошибок</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,6 +231,21 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -181,7 +295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -194,6 +308,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,13 +626,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38262EF8-86AA-4B81-8C63-A8D11CCB537D}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="85.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="59.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -526,7 +644,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -534,7 +652,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -542,7 +660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -550,7 +668,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
@@ -558,7 +676,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -566,7 +684,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -574,7 +692,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -582,7 +700,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
@@ -590,7 +708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
@@ -598,7 +716,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
@@ -606,7 +724,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
@@ -614,15 +732,135 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>1</v>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/nomenclature.xlsx
+++ b/data/nomenclature.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NSI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB35363F-6135-4902-B910-71514F9E7456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193D892E-E493-4139-B353-760CD9327AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B6179685-600B-43B7-9873-FF275DBDA963}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{B6179685-600B-43B7-9873-FF275DBDA963}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>артикул</t>
   </si>
@@ -211,6 +211,15 @@
   </si>
   <si>
     <t>Винт 5-26-Хим.Пас-ОСТ 1 31503-80                 нет ошибок</t>
+  </si>
+  <si>
+    <t>Болт (2)-12-44-Фос.Окс.ЭФП-ОСТ 1 31133-80</t>
+  </si>
+  <si>
+    <t>Болт (2)-12-96-Фос.Окс.ЭФП-ОСТ 1 31133-80</t>
+  </si>
+  <si>
+    <t>Болт (2)-8-26-Кд-ОСТ 1 31133-80</t>
   </si>
 </sst>
 </file>
@@ -295,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -311,6 +320,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -629,7 +641,7 @@
   <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="85.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.28515625" customWidth="1"/>
     <col min="4" max="4" width="59.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -651,6 +663,9 @@
       <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
+      <c r="D2" s="6" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -659,6 +674,9 @@
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="D3" s="6" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -666,6 +684,9 @@
       </c>
       <c r="B4" s="4" t="s">
         <v>7</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">

--- a/data/nomenclature.xlsx
+++ b/data/nomenclature.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NSI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193D892E-E493-4139-B353-760CD9327AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA33DC1C-BD48-4139-B2ED-13A7E33EAE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{B6179685-600B-43B7-9873-FF275DBDA963}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="17520" xr2:uid="{B6179685-600B-43B7-9873-FF275DBDA963}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="68">
   <si>
     <t>артикул</t>
   </si>
@@ -111,9 +111,6 @@
     <t>Болт 2M12x1,25-6gx100.58 ГОСТ 7795-70</t>
   </si>
   <si>
-    <t>GUID</t>
-  </si>
-  <si>
     <t>Болт 4-14-Ан.Окс-ОСТ 1 31141-80</t>
   </si>
   <si>
@@ -183,9 +180,6 @@
     <t>7594612323.006</t>
   </si>
   <si>
-    <t>Болт 5-16-Ц-ОСТ 1 31140-80                               нет ошибок</t>
-  </si>
-  <si>
     <t>Винт 4-10-Кд.фос.окс-ОСТ 1 31552-80             нет ошибок</t>
   </si>
   <si>
@@ -220,6 +214,30 @@
   </si>
   <si>
     <t>Болт (2)-8-26-Кд-ОСТ 1 31133-80</t>
+  </si>
+  <si>
+    <t>Болт (2)-8-32-Кд-ОСТ 1 31133-80</t>
+  </si>
+  <si>
+    <t>Болт (2)-8-34-Кд-ОСТ 1 31133-80</t>
+  </si>
+  <si>
+    <t>Винт (4)-5-10-Хим.Пас-ОСТ 1 31503-80</t>
+  </si>
+  <si>
+    <t>Винт (4)-5-12-Хим.Пас-ОСТ 1 31503-80</t>
+  </si>
+  <si>
+    <t>Винт (4)-5-14-Хим.Пас-ОСТ 1 31503-80</t>
+  </si>
+  <si>
+    <t>Номенклатура в ЕНС</t>
+  </si>
+  <si>
+    <t>Комментарий</t>
+  </si>
+  <si>
+    <t>Винт 4-10-Кд.фос.окс-ОСТ 1 31552-80 </t>
   </si>
 </sst>
 </file>
@@ -638,25 +656,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38262EF8-86AA-4B81-8C63-A8D11CCB537D}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.28515625" customWidth="1"/>
     <col min="4" max="4" width="59.28515625" customWidth="1"/>
+    <col min="5" max="5" width="64.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -664,10 +686,10 @@
         <v>3</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -675,10 +697,10 @@
         <v>5</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -686,58 +708,74 @@
         <v>7</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D5" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D6" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D8" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D9" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D10" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
@@ -745,7 +783,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
@@ -753,130 +791,152 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="5" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="5" t="s">
+    <row r="19" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="5" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="5" t="s">
+    <row r="21" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="5" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="5" t="s">
+    <row r="23" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="5" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/data/nomenclature.xlsx
+++ b/data/nomenclature.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NSI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA33DC1C-BD48-4139-B2ED-13A7E33EAE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCA55C4-A322-4A23-8686-B6BAACB1D290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="17520" xr2:uid="{B6179685-600B-43B7-9873-FF275DBDA963}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B6179685-600B-43B7-9873-FF275DBDA963}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -34,77 +34,41 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="68">
-  <si>
-    <t>артикул</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
   <si>
     <t>Краткое наименование</t>
   </si>
   <si>
-    <t>759128Х009.000</t>
-  </si>
-  <si>
     <t>Болт (2)-12-44-Окс.Фос.ЭФП-ОСТ 1 31133-80,</t>
   </si>
   <si>
-    <t>759129Х022.000</t>
-  </si>
-  <si>
     <t>Болт (2)-12-96-Окс.Фос.ЭФП-ОСТ 1 31133-80,</t>
   </si>
   <si>
-    <t>7591291091.000</t>
-  </si>
-  <si>
     <t>Болт (2)-8-26-Кд-ОСТ 1 31133-80,</t>
   </si>
   <si>
-    <t>7591291095.000</t>
-  </si>
-  <si>
     <t>Болт (2)-8-34-Кд-ОСТ 1 31133-80,</t>
   </si>
   <si>
-    <t>7592126307.000</t>
-  </si>
-  <si>
     <t>Винт (3)-6-46-Кд-ОСТ 1 31502-80,</t>
   </si>
   <si>
-    <t>7594602323.000</t>
-  </si>
-  <si>
     <t>Шайба 0,5-4-8-Кд-ОСТ 1 34505-80,</t>
   </si>
   <si>
-    <t>7594612323.000</t>
-  </si>
-  <si>
     <t>Шайба 0,5-4-8-Кд-ОСТ 1 34507-80,</t>
   </si>
   <si>
-    <t>7591291094.000</t>
-  </si>
-  <si>
     <t>Болт (2)-8-32-Кд-ОСТ 1 31133-80,</t>
   </si>
   <si>
-    <t>7592134065.000</t>
-  </si>
-  <si>
     <t>Винт (4)-5-10-Хим.Пас-ОСТ 1 31503-80,</t>
   </si>
   <si>
-    <t>7592134067.000</t>
-  </si>
-  <si>
     <t>Винт (4)-5-12-Хим.Пас-ОСТ 1 31503-80,</t>
   </si>
   <si>
-    <t>7592134068.000</t>
-  </si>
-  <si>
     <t>Винт (4)-5-14-Хим.Пас-ОСТ 1 31503-80,</t>
   </si>
   <si>
@@ -120,9 +84,6 @@
     <t>Винт 4-10-Кд.фос.окс-ОСТ 1 31552-80</t>
   </si>
   <si>
-    <t>Винт 3-6-Кд-ОСТ 1 31509-80</t>
-  </si>
-  <si>
     <t>Винт 3-12-Хим.Пас-ОСТ 1 31509-80</t>
   </si>
   <si>
@@ -144,42 +105,6 @@
     <t>Винт 5-26-Хим.Пас-ОСТ 1 31503-80</t>
   </si>
   <si>
-    <t>7594602323.001</t>
-  </si>
-  <si>
-    <t>7594612323.001</t>
-  </si>
-  <si>
-    <t>7594602323.002</t>
-  </si>
-  <si>
-    <t>7594612323.002</t>
-  </si>
-  <si>
-    <t>7594602323.003</t>
-  </si>
-  <si>
-    <t>7594612323.003</t>
-  </si>
-  <si>
-    <t>7594602323.004</t>
-  </si>
-  <si>
-    <t>7594612323.004</t>
-  </si>
-  <si>
-    <t>7594602323.005</t>
-  </si>
-  <si>
-    <t>7594612323.005</t>
-  </si>
-  <si>
-    <t>7594602323.006</t>
-  </si>
-  <si>
-    <t>7594612323.006</t>
-  </si>
-  <si>
     <t>Винт 4-10-Кд.фос.окс-ОСТ 1 31552-80             нет ошибок</t>
   </si>
   <si>
@@ -238,6 +163,15 @@
   </si>
   <si>
     <t>Винт 4-10-Кд.фос.окс-ОСТ 1 31552-80 </t>
+  </si>
+  <si>
+    <t> Винт 3-6-Кд-ОСТ 1 31509-80</t>
+  </si>
+  <si>
+    <t>Винт (3)-6-46-Кд-ОСТ 1 31502-80</t>
+  </si>
+  <si>
+    <t>Шайба 0,5-4-8-Кд-ОСТ1 34505-80</t>
   </si>
 </sst>
 </file>
@@ -322,16 +256,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -656,287 +584,223 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38262EF8-86AA-4B81-8C63-A8D11CCB537D}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="42.28515625" customWidth="1"/>
-    <col min="4" max="4" width="59.28515625" customWidth="1"/>
-    <col min="5" max="5" width="64.5703125" customWidth="1"/>
+    <col min="1" max="1" width="42.28515625" customWidth="1"/>
+    <col min="2" max="2" width="59.28515625" customWidth="1"/>
+    <col min="3" max="3" width="64.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B4" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B6" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="B7" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B11" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="B12" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/data/nomenclature.xlsx
+++ b/data/nomenclature.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NSI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCA55C4-A322-4A23-8686-B6BAACB1D290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79DD8A15-A84A-4BA6-9362-BC70157C9CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B6179685-600B-43B7-9873-FF275DBDA963}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="17520" xr2:uid="{B6179685-600B-43B7-9873-FF275DBDA963}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
   <si>
     <t>Краткое наименование</t>
   </si>
@@ -172,6 +172,15 @@
   </si>
   <si>
     <t>Шайба 0,5-4-8-Кд-ОСТ1 34505-80</t>
+  </si>
+  <si>
+    <t>Болт 2М10-110 ГОСТ 7798-70</t>
+  </si>
+  <si>
+    <t>Болт 4-12-Хим.Пас-ОСТ 1 31104-80,</t>
+  </si>
+  <si>
+    <t>Гайка 22-Хим.Пас-ОСТ 1 33049-80,</t>
   </si>
 </sst>
 </file>
@@ -584,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38262EF8-86AA-4B81-8C63-A8D11CCB537D}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.28515625" customWidth="1"/>
@@ -803,6 +812,21 @@
         <v>31</v>
       </c>
     </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
